--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/ene-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/ene-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>8665.02</v>
+        <v>8496.02</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>14759.35</v>
+        <v>14414.08</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>12754.04</v>
+        <v>12571.24</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7616.64</v>
+        <v>7507.47</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8049.98</v>
+        <v>7933.97</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>24737.91</v>
+        <v>24689.2</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>7966.42</v>
+        <v>7950.73</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>23958.25</v>
+        <v>23911.07</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>19027.01</v>
+        <v>19027.13</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>16065.98</v>
+        <v>16066.08</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>11839.25</v>
+        <v>11855.69</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>27399.77</v>
+        <v>27381.05</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>50009.4</v>
+        <v>49975.24</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>20770.04</v>
+        <v>20755.85</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>7723.86</v>
+        <v>7718.58</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>42223.75</v>
+        <v>42194.91</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>15433.58</v>
+        <v>15380.61</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>29035.98</v>
+        <v>28936.33</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>66313.67</v>
+        <v>65963.37</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>7000.93</v>
+        <v>6963.95</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>51300.07</v>
+        <v>51029.08</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>11099.08</v>
+        <v>11029.53</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>37550.49</v>
+        <v>37796.6</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>10893.73</v>
+        <v>11040.43</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>14928.99</v>
+        <v>15156.27</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>21023.71</v>
+        <v>21343.78</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>24099.27</v>
+        <v>24466.16</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>11843.25</v>
+        <v>12131.25</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>109064.12</v>
+        <v>111821.26</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>16669.26</v>
+        <v>17090.66</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>57209.18</v>
+        <v>58655.43</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>6716.9</v>
+        <v>6886.7</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>23035.75</v>
+        <v>23734.26</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>6708.55</v>
+        <v>6907.95</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>10567.04</v>
+        <v>10881.13</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>6007.44</v>
+        <v>6186</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>57567.96</v>
+        <v>59279.05</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/ene-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/ene-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/ene-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/ene-2026.xlsx
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fondos Extrapresupuestarios Escipol</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fondos Extrapresupuestarios Escipol</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2313,7 +2313,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fondos Extrapresupuestarios Escipol</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">

--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/ene-2026.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/ene-2026.xlsx
@@ -562,7 +562,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>77.472.821-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>76.058.118-6</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>76.465.697-0</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1196,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1383,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1631,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1818,11 @@
           <t>77.599.784-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2005,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2192,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2318,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2383,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2509,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2574,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2639,11 @@
           <t>77.018.060-0</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2704,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2769,11 @@
           <t>77.547.481-5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
